--- a/TestData/TestData.xlsx
+++ b/TestData/TestData.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\STZ\eclipse-workspace\Swag-Lab-Project\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\STZ\EclipsWorkspace\NewSwagLab_Project\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E96B6760-85DA-4D1D-A4E0-5EFA965EE910}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CC79970-13FC-4A59-B7F1-3DEBD804AE95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="29">
   <si>
     <t>standard_user</t>
   </si>
@@ -107,6 +107,21 @@
   </si>
   <si>
     <t>Sauce Labs Fleece Jacket</t>
+  </si>
+  <si>
+    <t>Element</t>
+  </si>
+  <si>
+    <t>Sauce_Labs_Backpack</t>
+  </si>
+  <si>
+    <t>Sauce_Labs_Bolt_T_Shirt</t>
+  </si>
+  <si>
+    <t>Sauce_Labs_Onesie</t>
+  </si>
+  <si>
+    <t>Sauce_Labs_Fleece_Jacket</t>
   </si>
 </sst>
 </file>
@@ -116,7 +131,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -145,6 +160,19 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF2A00FF"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="3">
@@ -202,7 +230,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -229,9 +257,11 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -577,17 +607,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5547A6D9-B35F-4592-972E-BF4A3E31F7BE}">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="31.88671875" customWidth="1"/>
     <col min="2" max="2" width="21.88671875" customWidth="1"/>
     <col min="3" max="3" width="24" customWidth="1"/>
     <col min="4" max="4" width="8.88671875" style="11"/>
-    <col min="5" max="5" width="15.6640625" customWidth="1"/>
+    <col min="5" max="5" width="24" customWidth="1"/>
+    <col min="9" max="9" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>4</v>
       </c>
@@ -600,8 +631,14 @@
       <c r="D1" s="9" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>14</v>
       </c>
@@ -614,8 +651,14 @@
       <c r="D2" s="10">
         <v>29.99</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E2" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I2" s="14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
         <v>15</v>
       </c>
@@ -628,8 +671,11 @@
       <c r="D3" s="10">
         <v>15.99</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E3" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>19</v>
       </c>
@@ -642,8 +688,11 @@
       <c r="D4" s="10">
         <v>7.99</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E4" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
         <v>22</v>
       </c>
@@ -656,8 +705,11 @@
       <c r="D5" s="12">
         <v>49.99</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E5" s="8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
         <v>20</v>
       </c>
@@ -670,8 +722,16 @@
       <c r="D6" s="10">
         <v>15.99</v>
       </c>
+      <c r="E6" s="13" t="s">
+        <v>26</v>
+      </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B6" xr:uid="{03A4D82A-9428-4A28-800B-B1FE8D21414E}">
+      <formula1>$I$1:$I$2</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/TestData/TestData.xlsx
+++ b/TestData/TestData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\STZ\EclipsWorkspace\NewSwagLab_Project\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CC79970-13FC-4A59-B7F1-3DEBD804AE95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85F6BC1A-6FA3-4048-8E72-5C01EF00F3DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="30">
   <si>
     <t>standard_user</t>
   </si>
@@ -122,6 +122,9 @@
   </si>
   <si>
     <t>Sauce_Labs_Fleece_Jacket</t>
+  </si>
+  <si>
+    <t>Fifth Item Purchase</t>
   </si>
 </sst>
 </file>
@@ -607,7 +610,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5547A6D9-B35F-4592-972E-BF4A3E31F7BE}">
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="31.88671875" customWidth="1"/>
@@ -726,9 +729,26 @@
         <v>26</v>
       </c>
     </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="10">
+        <v>15.99</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B6" xr:uid="{03A4D82A-9428-4A28-800B-B1FE8D21414E}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B7" xr:uid="{03A4D82A-9428-4A28-800B-B1FE8D21414E}">
       <formula1>$I$1:$I$2</formula1>
     </dataValidation>
   </dataValidations>
